--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AUTOMYND\Documents\UiPath\CLQ002_AxessPatientChartRetrieval\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5635C1-BFAC-4EB0-A3C3-57A5CB584F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3155AB1D-CB29-4554-9FE4-A15C7FACFADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -2309,7 +2309,7 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
@@ -2423,7 +2423,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>41</v>
